--- a/data/trans_orig/P1438_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1438_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de otro dolor crónico en 2023</t>
+          <t>Población con diagnóstico de otro dolor crónico en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15592</t>
+          <t>16618</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14401</t>
+          <t>13986</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11572</t>
+          <t>12395</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25950</t>
+          <t>25737</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>295851</t>
+          <t>294825</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>307213</t>
+          <t>307050</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275234</t>
+          <t>275649</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283885</t>
+          <t>284006</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>575127</t>
+          <t>575340</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>589505</t>
+          <t>588682</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14365</t>
+          <t>13955</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35314</t>
+          <t>36326</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>29283</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49406</t>
+          <t>49465</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48373</t>
+          <t>47710</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77211</t>
+          <t>76810</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>482079</t>
+          <t>481067</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>503028</t>
+          <t>503438</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464885</t>
+          <t>464826</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>484771</t>
+          <t>485008</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>954473</t>
+          <t>954874</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>983311</t>
+          <t>983974</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22303</t>
+          <t>22125</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41108</t>
+          <t>40535</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48708</t>
+          <t>50146</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70460</t>
+          <t>72197</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>77073</t>
+          <t>77136</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104849</t>
+          <t>105493</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>274942</t>
+          <t>275515</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>293747</t>
+          <t>293925</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>278668</t>
+          <t>276931</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>300420</t>
+          <t>298982</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>560329</t>
+          <t>559685</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>588105</t>
+          <t>588042</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,4%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9345</t>
+          <t>9484</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25910</t>
+          <t>25446</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15890</t>
+          <t>16690</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38868</t>
+          <t>39304</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29741</t>
+          <t>30139</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56676</t>
+          <t>57085</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>286647</t>
+          <t>287111</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>303212</t>
+          <t>303073</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>436850</t>
+          <t>436414</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>459828</t>
+          <t>459028</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>731598</t>
+          <t>731189</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>758533</t>
+          <t>758135</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12112</t>
+          <t>11266</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13488</t>
+          <t>13527</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24290</t>
+          <t>24217</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18887</t>
+          <t>19101</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32123</t>
+          <t>32686</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>166630</t>
+          <t>167476</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175038</t>
+          <t>175090</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>183984</t>
+          <t>184057</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>194786</t>
+          <t>194747</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>354893</t>
+          <t>354330</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>368129</t>
+          <t>367915</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27948</t>
+          <t>28283</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46167</t>
+          <t>45059</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42290</t>
+          <t>42507</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61265</t>
+          <t>60461</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74509</t>
+          <t>75839</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>99413</t>
+          <t>101575</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>223469</t>
+          <t>224577</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>241688</t>
+          <t>241353</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>195122</t>
+          <t>195926</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>214097</t>
+          <t>213880</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>426610</t>
+          <t>424448</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>451514</t>
+          <t>450184</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,58%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11893</t>
+          <t>12046</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27772</t>
+          <t>28806</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22964</t>
+          <t>23563</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>76411</t>
+          <t>76452</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42763</t>
+          <t>46384</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90678</t>
+          <t>90662</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>594109</t>
+          <t>593075</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>609988</t>
+          <t>609835</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>772535</t>
+          <t>772494</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>825982</t>
+          <t>825383</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1380149</t>
+          <t>1380165</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1428064</t>
+          <t>1424443</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21189</t>
+          <t>21407</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24587</t>
+          <t>25042</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41995</t>
+          <t>41185</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27069</t>
+          <t>27576</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57746</t>
+          <t>58916</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>907531</t>
+          <t>907313</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>924145</t>
+          <t>924341</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>673397</t>
+          <t>674207</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>690805</t>
+          <t>690350</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1586366</t>
+          <t>1585196</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1617043</t>
+          <t>1616536</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>118258</t>
+          <t>118186</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>177835</t>
+          <t>178489</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>239466</t>
+          <t>233275</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>319636</t>
+          <t>322918</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>390812</t>
+          <t>382468</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>488338</t>
+          <t>485284</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3278587</t>
+          <t>3277933</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3338164</t>
+          <t>3338236</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3338132</t>
+          <t>3334850</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3418302</t>
+          <t>3424493</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6625852</t>
+          <t>6628906</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6723378</t>
+          <t>6731722</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1438_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1438_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8661</t>
+          <t>8827</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16618</t>
+          <t>15468</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9141</t>
+          <t>10023</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>6248</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13986</t>
+          <t>15293</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>17803</t>
+          <t>18851</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12395</t>
+          <t>12959</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25737</t>
+          <t>26710</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>302782</t>
+          <t>310018</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>294825</t>
+          <t>303377</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>307050</t>
+          <t>314224</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>280494</t>
+          <t>306038</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275649</t>
+          <t>300768</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284006</t>
+          <t>309813</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>583274</t>
+          <t>616055</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>575340</t>
+          <t>608196</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>588682</t>
+          <t>621947</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23441</t>
+          <t>25073</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13955</t>
+          <t>15470</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36326</t>
+          <t>37433</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38416</t>
+          <t>40479</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29283</t>
+          <t>31000</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49465</t>
+          <t>52597</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>61857</t>
+          <t>65552</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47710</t>
+          <t>51461</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76810</t>
+          <t>82792</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>493952</t>
+          <t>504587</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>481067</t>
+          <t>492227</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>503438</t>
+          <t>514190</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>475875</t>
+          <t>505330</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464826</t>
+          <t>493212</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>485008</t>
+          <t>514809</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>969827</t>
+          <t>1009917</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>954874</t>
+          <t>992677</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>983974</t>
+          <t>1024008</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031684</t>
+          <t>1075469</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031684</t>
+          <t>1075469</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031684</t>
+          <t>1075469</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>30412</t>
+          <t>31147</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22125</t>
+          <t>23189</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40535</t>
+          <t>40718</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>59539</t>
+          <t>60252</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50146</t>
+          <t>49376</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72197</t>
+          <t>71176</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>89950</t>
+          <t>91399</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>77136</t>
+          <t>78691</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105493</t>
+          <t>105829</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>285638</t>
+          <t>284846</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>275515</t>
+          <t>275275</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>293925</t>
+          <t>292804</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>289589</t>
+          <t>296129</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>276931</t>
+          <t>285205</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>298982</t>
+          <t>307005</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>575228</t>
+          <t>580976</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>559685</t>
+          <t>566546</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>588042</t>
+          <t>593684</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,3%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15396</t>
+          <t>17053</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9484</t>
+          <t>10272</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25446</t>
+          <t>28586</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28222</t>
+          <t>32267</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16690</t>
+          <t>24536</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39304</t>
+          <t>41308</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>43619</t>
+          <t>49320</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30139</t>
+          <t>38200</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57085</t>
+          <t>62675</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>297161</t>
+          <t>356092</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>287111</t>
+          <t>344559</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>303073</t>
+          <t>362873</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>447496</t>
+          <t>389694</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>436414</t>
+          <t>380653</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>459028</t>
+          <t>397425</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>744655</t>
+          <t>745787</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>731189</t>
+          <t>732432</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>758135</t>
+          <t>756907</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6912</t>
+          <t>7352</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11266</t>
+          <t>12840</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18143</t>
+          <t>19328</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13527</t>
+          <t>13937</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24217</t>
+          <t>25081</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>25054</t>
+          <t>26681</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19101</t>
+          <t>20412</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32686</t>
+          <t>35206</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>171830</t>
+          <t>198313</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167476</t>
+          <t>192825</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175090</t>
+          <t>201537</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>190131</t>
+          <t>207495</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>184057</t>
+          <t>201742</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>194747</t>
+          <t>212886</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>361962</t>
+          <t>405807</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>354330</t>
+          <t>397282</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>367915</t>
+          <t>412076</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>36226</t>
+          <t>36413</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28283</t>
+          <t>28763</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45059</t>
+          <t>46213</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>50839</t>
+          <t>51662</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42507</t>
+          <t>42499</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60461</t>
+          <t>61028</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>87065</t>
+          <t>88076</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>75839</t>
+          <t>76058</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101575</t>
+          <t>101663</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>233410</t>
+          <t>234294</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224577</t>
+          <t>224494</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>241353</t>
+          <t>241944</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>205548</t>
+          <t>211437</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>195926</t>
+          <t>202071</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>213880</t>
+          <t>220600</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>438958</t>
+          <t>445730</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>424448</t>
+          <t>432143</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>450184</t>
+          <t>457748</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,75%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>19267</t>
+          <t>23763</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12046</t>
+          <t>15554</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28806</t>
+          <t>34727</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>52922</t>
+          <t>67334</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23563</t>
+          <t>55493</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>76452</t>
+          <t>81695</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>72189</t>
+          <t>91097</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46384</t>
+          <t>76311</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90662</t>
+          <t>111380</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>602614</t>
+          <t>693187</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>593075</t>
+          <t>682223</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>609835</t>
+          <t>701396</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>796024</t>
+          <t>703372</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>772494</t>
+          <t>689011</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>825383</t>
+          <t>715213</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1398638</t>
+          <t>1396558</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1380165</t>
+          <t>1376275</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1424443</t>
+          <t>1411344</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>621881</t>
+          <t>716950</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>621881</t>
+          <t>716950</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>621881</t>
+          <t>716950</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>848946</t>
+          <t>770706</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>848946</t>
+          <t>770706</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>848946</t>
+          <t>770706</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1470827</t>
+          <t>1487655</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1470827</t>
+          <t>1487655</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1470827</t>
+          <t>1487655</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>12413</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4379</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21407</t>
+          <t>22849</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>32118</t>
+          <t>36988</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25042</t>
+          <t>28337</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>47910</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>44531</t>
+          <t>51089</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27576</t>
+          <t>40199</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>58916</t>
+          <t>65199</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>916307</t>
+          <t>783971</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>907313</t>
+          <t>775223</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>924341</t>
+          <t>789832</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>683274</t>
+          <t>793621</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>674207</t>
+          <t>782699</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>690350</t>
+          <t>802272</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1599581</t>
+          <t>1577592</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1585196</t>
+          <t>1563482</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1616536</t>
+          <t>1588482</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>152728</t>
+          <t>163729</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>118186</t>
+          <t>142231</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>178489</t>
+          <t>187382</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>289340</t>
+          <t>318334</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>233275</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>322918</t>
+          <t>346789</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>442068</t>
+          <t>482063</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>382468</t>
+          <t>448195</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>485284</t>
+          <t>519194</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3303694</t>
+          <t>3365308</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3277933</t>
+          <t>3341655</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3338236</t>
+          <t>3386806</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3368428</t>
+          <t>3413116</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3334850</t>
+          <t>3384661</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3424493</t>
+          <t>3436084</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6672122</t>
+          <t>6778424</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6628906</t>
+          <t>6741293</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6731722</t>
+          <t>6812292</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>93,83%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3456422</t>
+          <t>3529037</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3456422</t>
+          <t>3529037</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3456422</t>
+          <t>3529037</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3657768</t>
+          <t>3731450</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3657768</t>
+          <t>3731450</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3657768</t>
+          <t>3731450</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7114190</t>
+          <t>7260487</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7114190</t>
+          <t>7260487</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7114190</t>
+          <t>7260487</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
